--- a/reports/tables/DCA_Analysis_FirstVisit_Model.xlsx
+++ b/reports/tables/DCA_Analysis_FirstVisit_Model.xlsx
@@ -455,7 +455,7 @@
         <v>0.01</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05686682571104682</v>
+        <v>0.06131668443226232</v>
       </c>
       <c r="C2" t="n">
         <v>0.05926941102820499</v>
@@ -469,7 +469,7 @@
         <v>0.01482758620689655</v>
       </c>
       <c r="B3" t="n">
-        <v>0.05272131278255705</v>
+        <v>0.05771008818447622</v>
       </c>
       <c r="C3" t="n">
         <v>0.05465960065172438</v>
@@ -483,7 +483,7 @@
         <v>0.0196551724137931</v>
       </c>
       <c r="B4" t="n">
-        <v>0.04853497172814478</v>
+        <v>0.05239292959109063</v>
       </c>
       <c r="C4" t="n">
         <v>0.05000438939921792</v>
@@ -497,7 +497,7 @@
         <v>0.02448275862068965</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04430719640384082</v>
+        <v>0.04061132811459205</v>
       </c>
       <c r="C5" t="n">
         <v>0.04530310323859192</v>
@@ -511,7 +511,7 @@
         <v>0.0293103448275862</v>
       </c>
       <c r="B6" t="n">
-        <v>0.03138546492081486</v>
+        <v>0.03807373159462202</v>
       </c>
       <c r="C6" t="n">
         <v>0.04055505472894372</v>
@@ -525,7 +525,7 @@
         <v>0.03413793103448275</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02816833184128426</v>
+        <v>0.03542584994471346</v>
       </c>
       <c r="C7" t="n">
         <v>0.03575954268546111</v>
@@ -539,7 +539,7 @@
         <v>0.03896551724137931</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02491887736734143</v>
+        <v>0.03281928119247114</v>
       </c>
       <c r="C8" t="n">
         <v>0.03091585183422194</v>
@@ -553,7 +553,7 @@
         <v>0.04379310344827586</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02163661195749151</v>
+        <v>0.02363059437106195</v>
       </c>
       <c r="C9" t="n">
         <v>0.0260232524565368</v>
@@ -567,7 +567,7 @@
         <v>0.04862068965517241</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0232860569611377</v>
+        <v>0.02171058263408379</v>
       </c>
       <c r="C10" t="n">
         <v>0.02108100002246341</v>
@@ -581,7 +581,7 @@
         <v>0.05344827586206896</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02045747865008102</v>
+        <v>0.01977098607793064</v>
       </c>
       <c r="C11" t="n">
         <v>0.01608833481310622</v>
@@ -595,7 +595,7 @@
         <v>0.05827586206896551</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01473926449040025</v>
+        <v>0.01781150350801978</v>
       </c>
       <c r="C12" t="n">
         <v>0.01104448153129863</v>
@@ -609,7 +609,7 @@
         <v>0.06310344827586206</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01308036933532834</v>
+        <v>0.01594464778807545</v>
       </c>
       <c r="C13" t="n">
         <v>0.005948648900249015</v>
@@ -623,7 +623,7 @@
         <v>0.06793103448275861</v>
       </c>
       <c r="B14" t="n">
-        <v>0.00855678069717189</v>
+        <v>0.01395372472177139</v>
       </c>
       <c r="C14" t="n">
         <v>0.0008000292497138684</v>
@@ -637,7 +637,7 @@
         <v>0.07275862068965516</v>
       </c>
       <c r="B15" t="n">
-        <v>0.007415283931745006</v>
+        <v>0.01194207058597812</v>
       </c>
       <c r="C15" t="n">
         <v>-0.004402201910756187</v>
@@ -651,7 +651,7 @@
         <v>0.07758620689655171</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00640273016171199</v>
+        <v>0.002332534948887743</v>
       </c>
       <c r="C16" t="n">
         <v>-0.009658886331971372</v>
@@ -665,7 +665,7 @@
         <v>0.08241379310344826</v>
       </c>
       <c r="B17" t="n">
-        <v>0.005246702005580955</v>
+        <v>0.001164534938251322</v>
       </c>
       <c r="C17" t="n">
         <v>-0.01497088347915199</v>
@@ -679,7 +679,7 @@
         <v>0.08724137931034481</v>
       </c>
       <c r="B18" t="n">
-        <v>0.004078445368765501</v>
+        <v>-0.0001582019150025392</v>
       </c>
       <c r="C18" t="n">
         <v>-0.02033907100038664</v>
@@ -693,7 +693,7 @@
         <v>0.09206896551724136</v>
       </c>
       <c r="B19" t="n">
-        <v>0.002897765190046957</v>
+        <v>-0.001495005092559898</v>
       </c>
       <c r="C19" t="n">
         <v>-0.02576434521003547</v>
@@ -707,7 +707,7 @@
         <v>0.09689655172413791</v>
       </c>
       <c r="B20" t="n">
-        <v>0.001704462237367317</v>
+        <v>-0.002846100171213707</v>
       </c>
       <c r="C20" t="n">
         <v>-0.0312476215876378</v>
@@ -721,7 +721,7 @@
         <v>0.1017241379310345</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0004983329957529183</v>
+        <v>-0.0009870208367493243</v>
       </c>
       <c r="C21" t="n">
         <v>-0.03678983529290726</v>
@@ -735,7 +735,7 @@
         <v>0.106551724137931</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.0007208304483953265</v>
+        <v>-0.002196108549954195</v>
       </c>
       <c r="C22" t="n">
         <v>-0.04239194169742315</v>
@@ -749,7 +749,7 @@
         <v>0.1113793103448276</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.001953240526783438</v>
+        <v>-0.003418333421082904</v>
       </c>
       <c r="C23" t="n">
         <v>-0.04805491693365284</v>
@@ -763,7 +763,7 @@
         <v>0.1162068965517241</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.003199114312621758</v>
+        <v>-0.005500254556695557</v>
       </c>
       <c r="C24" t="n">
         <v>-0.05377975846196777</v>
@@ -777,7 +777,7 @@
         <v>0.1210344827586207</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.004458673648088749</v>
+        <v>-0.00615605817764118</v>
       </c>
       <c r="C25" t="n">
         <v>-0.059567485656345</v>
@@ -791,7 +791,7 @@
         <v>0.1258620689655172</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.005732145276018487</v>
+        <v>-0.006819105388877325</v>
       </c>
       <c r="C26" t="n">
         <v>-0.0654191404094767</v>
@@ -805,7 +805,7 @@
         <v>0.1306896551724138</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.001270400661246202</v>
+        <v>-0.007489516869020496</v>
       </c>
       <c r="C27" t="n">
         <v>-0.07133578775804182</v>
@@ -819,7 +819,7 @@
         <v>0.1355172413793103</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.001276826894744965</v>
+        <v>-0.008167415992340374</v>
       </c>
       <c r="C28" t="n">
         <v>-0.07731851652892836</v>
@@ -833,7 +833,7 @@
         <v>0.1403448275862069</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.001537974670786746</v>
+        <v>-0.008852928904450049</v>
       </c>
       <c r="C29" t="n">
         <v>-0.08336844000722961</v>
@@ -847,7 +847,7 @@
         <v>0.1451724137931034</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.001802072078828997</v>
+        <v>-0.009546184600560958</v>
       </c>
       <c r="C30" t="n">
         <v>-0.0894866966268751</v>
@@ -861,7 +861,7 @@
         <v>0.15</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.002069169376293231</v>
+        <v>-0.01024731500640457</v>
       </c>
       <c r="C31" t="n">
         <v>-0.09567445068479653</v>
